--- a/docs/switch-research/click-and-thock-switches.xlsx
+++ b/docs/switch-research/click-and-thock-switches.xlsx
@@ -10344,7 +10344,9 @@
         <v>40</v>
       </c>
       <c r="F133" s="2" t="n"/>
-      <c r="G133" s="2" t="n"/>
+      <c r="G133" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n">
         <v>3.5</v>
@@ -10354,11 +10356,29 @@
           <t>deep, thocky</t>
         </is>
       </c>
-      <c r="K133" s="4" t="n"/>
-      <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr"/>
-      <c r="N133" s="2" t="inlineStr"/>
-      <c r="O133" s="2" t="inlineStr"/>
+      <c r="K133" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>USD 1.35 / 1 (DIYKEY, after 10% KBDNEWS code; 1.98 without)</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/GravaStar-UFO-switch-515.html</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P133" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=yIZyTdob7gg</t>
@@ -10377,7 +10397,7 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>pre-travel: adjustable</t>
+          <t>pre-travel: adjustable; filled 2026-10-19 from https://kbd.news/switch/GravaStar-UFO-switch-515.html</t>
         </is>
       </c>
     </row>
@@ -10420,11 +10440,29 @@
           <t>loud, clacky</t>
         </is>
       </c>
-      <c r="K134" s="4" t="n"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
+      <c r="K134" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.76 / 18 (Yogurt S variant; plain Yogurt not found in USD)</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>Divinikey</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
+        <is>
+          <t>https://divinikey.com/products/hmx-yogurt-s-linear-switches</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P134" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6WpG-La4jxw</t>
@@ -10482,11 +10520,29 @@
           <t>buttery</t>
         </is>
       </c>
-      <c r="K135" s="4" t="n"/>
-      <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr"/>
-      <c r="O135" s="2" t="inlineStr"/>
+      <c r="K135" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.75 / 10 (listing named Caramel Latte, V2 not confirmed; UniKeys V2 USD 2.79 / 10 sold out)</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/caramel-latte-vs-matcha-latte-v2</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P135" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mRvbMDnVR2Q</t>
@@ -10544,11 +10600,29 @@
           <t>creamy, loud, clacky</t>
         </is>
       </c>
-      <c r="K136" s="4" t="n"/>
-      <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
+      <c r="K136" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.79 / 10 (sale from 3.00; sold out)</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N136" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/grape-orange</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P136" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6xfHed_P2Aw</t>
@@ -10592,8 +10666,12 @@
         <v>45</v>
       </c>
       <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
-      <c r="H137" s="3" t="n"/>
+      <c r="G137" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I137" s="3" t="n">
         <v>3.6</v>
       </c>
@@ -10602,11 +10680,29 @@
           <t>creamy</t>
         </is>
       </c>
-      <c r="K137" s="4" t="n"/>
-      <c r="L137" s="2" t="inlineStr"/>
-      <c r="M137" s="2" t="inlineStr"/>
-      <c r="N137" s="2" t="inlineStr"/>
-      <c r="O137" s="2" t="inlineStr"/>
+      <c r="K137" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.99 / 10 (out of stock)</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N137" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/matcha-latte-v2</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P137" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=MX6Q180tgHg</t>
@@ -10623,7 +10719,11 @@
           <t>https://www.whatgeek.com/products/huano-matcha-latte-v2-linear-switch</t>
         </is>
       </c>
-      <c r="T137" s="2" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://thoccexchange.com/products/huano-matcha-latte-v2-linear-switches-10-pack</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -10658,17 +10758,37 @@
       <c r="H138" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="I138" s="3" t="n"/>
+      <c r="I138" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
           <t>deep</t>
         </is>
       </c>
-      <c r="K138" s="4" t="n"/>
-      <c r="L138" s="2" t="inlineStr"/>
-      <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr"/>
+      <c r="K138" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>USD 35.00 / 70 (sold out)</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Corsair (Drop)</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
+        <is>
+          <t>https://www.corsair.com/us/en/p/gaming-gear-accessories/dh-9917002-ww/drop-halo-true-mechanical-switches-dh-9917002-ww</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P138" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=iJh6-92HJhA</t>
@@ -10685,7 +10805,11 @@
           <t>https://deskthority.net/wiki/Input_Club_Halo</t>
         </is>
       </c>
-      <c r="T138" s="2" t="inlineStr"/>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://hirosarts.com/blog/halo-true-vs-halo-clear-switches/</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -10722,11 +10846,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K139" s="4" t="n"/>
-      <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="2" t="inlineStr"/>
-      <c r="N139" s="2" t="inlineStr"/>
-      <c r="O139" s="2" t="inlineStr"/>
+      <c r="K139" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.59 / 10</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N139" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/honey-bean-vs-salt-ice</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P139" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=eZetKBfq-k0</t>
@@ -10771,7 +10913,9 @@
       </c>
       <c r="F140" s="2" t="n"/>
       <c r="G140" s="2" t="n"/>
-      <c r="H140" s="3" t="n"/>
+      <c r="H140" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="I140" s="3" t="n">
         <v>3.4</v>
       </c>
@@ -10780,11 +10924,29 @@
           <t>silky</t>
         </is>
       </c>
-      <c r="K140" s="4" t="n"/>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr"/>
+      <c r="K140" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.59 / 10</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/poseidon-vs-yoel</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P140" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0eAnFKhsAFo</t>
@@ -10801,7 +10963,11 @@
           <t>https://milktooth.com/comparisons/poseidon-vs-sea-glass</t>
         </is>
       </c>
-      <c r="T140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://milktooth.com/comparisons/poseidon-vs-yoel</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10828,7 +10994,9 @@
         <v>42</v>
       </c>
       <c r="F141" s="2" t="n"/>
-      <c r="G141" s="2" t="n"/>
+      <c r="G141" s="2" t="n">
+        <v>42</v>
+      </c>
       <c r="H141" s="3" t="n">
         <v>1.2</v>
       </c>
@@ -10841,10 +11009,26 @@
         </is>
       </c>
       <c r="K141" s="4" t="n"/>
-      <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="2" t="inlineStr"/>
-      <c r="N141" s="2" t="inlineStr"/>
-      <c r="O141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>GBP 2.00 / 10 (UK only, no USD or CAD price found)</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>Thocc Exchange</t>
+        </is>
+      </c>
+      <c r="N141" s="5" t="inlineStr">
+        <is>
+          <t>https://thoccexchange.com/products/jerzzi-rainbow-switches-10-per-pack</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P141" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZnS1fILdem4</t>
@@ -10861,7 +11045,11 @@
           <t>https://thoccexchange.com/products/jerzzi-rainbow-switches-10-per-pack</t>
         </is>
       </c>
-      <c r="T141" s="2" t="inlineStr"/>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://keeb-finder.com/switches/compare/jerzzi-rainbow-switches-10-per-pack-vs-jerzzi-wind-rain</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10889,7 +11077,9 @@
       </c>
       <c r="F142" s="2" t="n"/>
       <c r="G142" s="2" t="n"/>
-      <c r="H142" s="3" t="n"/>
+      <c r="H142" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I142" s="3" t="n">
         <v>3.7</v>
       </c>
@@ -10898,11 +11088,29 @@
           <t>smooth</t>
         </is>
       </c>
-      <c r="K142" s="4" t="n"/>
-      <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr"/>
+      <c r="K142" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.30 / 10 (sale from 2.79; sold out)</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N142" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/violet</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P142" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5_tad802yBM</t>
@@ -10919,7 +11127,11 @@
           <t>https://milktooth.com/products/switches/violet</t>
         </is>
       </c>
-      <c r="T142" s="2" t="inlineStr"/>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://thoccexchange.com/products/jerzzi-violet-switches-10-per-pack</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10946,7 +11158,9 @@
         <v>40</v>
       </c>
       <c r="F143" s="2" t="n"/>
-      <c r="G143" s="2" t="n"/>
+      <c r="G143" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="H143" s="3" t="n">
         <v>1.6</v>
       </c>
@@ -10959,10 +11173,26 @@
         </is>
       </c>
       <c r="K143" s="4" t="n"/>
-      <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="2" t="inlineStr"/>
-      <c r="N143" s="2" t="inlineStr"/>
-      <c r="O143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>GBP 2.00 / 10 (no USD or CAD price found)</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>Thocc Exchange (UK)</t>
+        </is>
+      </c>
+      <c r="N143" s="5" t="inlineStr">
+        <is>
+          <t>https://thoccexchange.com/products/jerzzi-wind-rain</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P143" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=84ltPJBG4SM</t>
@@ -10979,7 +11209,11 @@
           <t>https://thoccexchange.com/products/jerzzi-wind-rain</t>
         </is>
       </c>
-      <c r="T143" s="2" t="inlineStr"/>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://keeb-finder.com/switches/compare/jerzzi-rainbow-switches-10-per-pack-vs-jerzzi-wind-rain</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -11008,7 +11242,9 @@
       <c r="F144" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G144" s="2" t="n"/>
+      <c r="G144" s="2" t="n">
+        <v>35</v>
+      </c>
       <c r="H144" s="3" t="n">
         <v>1.2</v>
       </c>
@@ -11020,11 +11256,29 @@
           <t>crisp</t>
         </is>
       </c>
-      <c r="K144" s="4" t="n"/>
-      <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr"/>
-      <c r="O144" s="2" t="inlineStr"/>
+      <c r="K144" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Focus Attack</t>
+        </is>
+      </c>
+      <c r="N144" s="5" t="inlineStr">
+        <is>
+          <t>https://focusattack.com/kailh-autumn-mini-clicky-low-profile-mx-switch/</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P144" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=bmKvAkFmrXE</t>
@@ -11043,7 +11297,7 @@
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>specs from maker site lookup</t>
+          <t>specs from maker site lookup; filled 2026-10-19 from https://www.rtings.com/keyboard-switch/reviews/kailh/autumn-mini</t>
         </is>
       </c>
     </row>
@@ -11084,11 +11338,29 @@
         <v>2.8</v>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="4" t="n"/>
-      <c r="L145" s="2" t="inlineStr"/>
-      <c r="M145" s="2" t="inlineStr"/>
-      <c r="N145" s="2" t="inlineStr"/>
-      <c r="O145" s="2" t="inlineStr"/>
+      <c r="K145" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.70 / 1</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>Keebio</t>
+        </is>
+      </c>
+      <c r="N145" s="5" t="inlineStr">
+        <is>
+          <t>https://keeb.io/products/kailh-choc-v2-low-profile-switches-mx-stem</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P145" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Qa1b4keSNks</t>
@@ -11135,8 +11407,12 @@
       <c r="E146" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
+      <c r="F146" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>60</v>
+      </c>
       <c r="H146" s="3" t="n">
         <v>1.8</v>
       </c>
@@ -11148,11 +11424,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K146" s="4" t="n"/>
-      <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="2" t="inlineStr"/>
-      <c r="O146" s="2" t="inlineStr"/>
+      <c r="K146" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.61 / 1 (pack size not stated)</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>MechanicalKeyboards.com</t>
+        </is>
+      </c>
+      <c r="N146" s="5" t="inlineStr">
+        <is>
+          <t>https://mechanicalkeyboards.com/collections/all?page=83</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P146" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=EGmdDaGKKbs</t>
@@ -11169,7 +11463,11 @@
           <t>https://keeb-finder.com/switches/compare/kailh-box-autumn-switch-9712744202540-vs-ttc-brother-v2-42g-clicky-pcb-mount-switch</t>
         </is>
       </c>
-      <c r="T146" s="2" t="inlineStr"/>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://comparigon.com/keyboard-switches/kailh-box-autumn</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -11192,17 +11490,47 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n"/>
+      <c r="E147" s="2" t="n">
+        <v>60</v>
+      </c>
       <c r="F147" s="2" t="n"/>
-      <c r="G147" s="2" t="n"/>
-      <c r="H147" s="3" t="n"/>
-      <c r="I147" s="3" t="n"/>
-      <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="4" t="n"/>
-      <c r="L147" s="2" t="inlineStr"/>
-      <c r="M147" s="2" t="inlineStr"/>
-      <c r="N147" s="2" t="inlineStr"/>
-      <c r="O147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>deep, muted</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.45 / 10</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>Thock King</t>
+        </is>
+      </c>
+      <c r="N147" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thockking.com/products/kailh-box-black-linear-switches</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P147" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=e3ANj8tzPFQ</t>
@@ -11215,7 +11543,11 @@
         </is>
       </c>
       <c r="S147" s="2" t="inlineStr"/>
-      <c r="T147" s="2" t="inlineStr"/>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://www.thockking.com/products/kailh-box-black-linear-switches</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -11255,10 +11587,18 @@
         </is>
       </c>
       <c r="K148" s="4" t="n"/>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M148" s="2" t="inlineStr"/>
       <c r="N148" s="2" t="inlineStr"/>
-      <c r="O148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P148" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=DVk1kvOTutA</t>
@@ -11318,11 +11658,29 @@
           <t>quiet</t>
         </is>
       </c>
-      <c r="K149" s="4" t="n"/>
-      <c r="L149" s="2" t="inlineStr"/>
-      <c r="M149" s="2" t="inlineStr"/>
-      <c r="N149" s="2" t="inlineStr"/>
-      <c r="O149" s="2" t="inlineStr"/>
+      <c r="K149" s="4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>CAD 52.99 / 110 (sold out; Box V2 Brown in stock CAD 65.99 / 110)</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>Keychron Canada</t>
+        </is>
+      </c>
+      <c r="N149" s="5" t="inlineStr">
+        <is>
+          <t>https://keychron.ca/products/kailh-box-switch-set</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P149" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Vu8Tiy3q-vM</t>
@@ -11382,11 +11740,29 @@
           <t>deep</t>
         </is>
       </c>
-      <c r="K150" s="4" t="n"/>
-      <c r="L150" s="2" t="inlineStr"/>
-      <c r="M150" s="2" t="inlineStr"/>
-      <c r="N150" s="2" t="inlineStr"/>
-      <c r="O150" s="2" t="inlineStr"/>
+      <c r="K150" s="4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>USD 39.99 / 110 (special price, was 46.99; Keychron G155 BOX Heavy set)</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>Central Computers</t>
+        </is>
+      </c>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.centralcomputer.com/keychron-g155-kailh-box-heavy-switch-burnt-orange-110-switches.html</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P150" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ClQmsujTLe0</t>
@@ -11439,12 +11815,34 @@
       <c r="I151" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J151" s="2" t="inlineStr"/>
-      <c r="K151" s="4" t="n"/>
-      <c r="L151" s="2" t="inlineStr"/>
-      <c r="M151" s="2" t="inlineStr"/>
-      <c r="N151" s="2" t="inlineStr"/>
-      <c r="O151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>clicky</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.58 / 1 (Kailh CN store, after KBDNEWS code)</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>Kailh store (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N151" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Box-Clicky-Switch-Full-POM-Crackle-Ice-switch-157.html</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P151" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-0yObz4yrzI</t>
@@ -11497,12 +11895,34 @@
       <c r="I152" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J152" s="2" t="inlineStr"/>
-      <c r="K152" s="4" t="n"/>
-      <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr"/>
-      <c r="O152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>clicky</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.73 / 1</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N152" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-BOX-Crystal-Jade-516.html</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P152" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sy5jm8SJfgo</t>
@@ -11560,11 +11980,29 @@
           <t>crisp</t>
         </is>
       </c>
-      <c r="K153" s="4" t="n"/>
-      <c r="L153" s="2" t="inlineStr"/>
-      <c r="M153" s="2" t="inlineStr"/>
-      <c r="N153" s="2" t="inlineStr"/>
-      <c r="O153" s="2" t="inlineStr"/>
+      <c r="K153" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>USD 67.99 / 110</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/collections/keyboard-switch/products/kailh-crystal-royal-box-tactile-switch</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P153" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mFdB7yHIwCE</t>
@@ -11610,7 +12048,9 @@
       <c r="F154" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G154" s="2" t="n"/>
+      <c r="G154" s="2" t="n">
+        <v>60</v>
+      </c>
       <c r="H154" s="3" t="n">
         <v>2</v>
       </c>
@@ -11622,11 +12062,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K154" s="4" t="n"/>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr"/>
-      <c r="O154" s="2" t="inlineStr"/>
+      <c r="K154" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>CAD 119.99 / 110 (sold out; Chosfox USD 50.68 / 110 in stock with KBDNEWS 5% code)</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Keychron Canada</t>
+        </is>
+      </c>
+      <c r="N154" s="5" t="inlineStr">
+        <is>
+          <t>https://keychron.ca/products/kailh-deep-sea-silent-pro-box-switch</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P154" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=pYUDDoI6XJ4</t>
@@ -11643,7 +12101,11 @@
           <t>https://www.keychron.com/products/kailh-deep-sea-silent-pro-box-switch</t>
         </is>
       </c>
-      <c r="T154" s="2" t="inlineStr"/>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://kbd.news/switch/Kailh-Deep-Sea-Silent-Pro-Box-Whale-199.html</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -11666,17 +12128,41 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n"/>
+      <c r="E155" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
-      <c r="H155" s="3" t="n"/>
-      <c r="I155" s="3" t="n"/>
+      <c r="H155" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="J155" s="2" t="inlineStr"/>
-      <c r="K155" s="4" t="n"/>
-      <c r="L155" s="2" t="inlineStr"/>
-      <c r="M155" s="2" t="inlineStr"/>
-      <c r="N155" s="2" t="inlineStr"/>
-      <c r="O155" s="2" t="inlineStr"/>
+      <c r="K155" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.54 / 1 (10% off with code KBDNEWS)</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N155" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Box-Jellyfish-PRO-Mengling-338.html</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P155" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=lGMBu6rcgsg</t>
@@ -11689,7 +12175,11 @@
         </is>
       </c>
       <c r="S155" s="2" t="inlineStr"/>
-      <c r="T155" s="2" t="inlineStr"/>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://kbd.news/switch/Kailh-Box-Jellyfish-PRO-Mengling-338.html</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -11731,10 +12221,26 @@
         </is>
       </c>
       <c r="K156" s="4" t="n"/>
-      <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr"/>
-      <c r="O156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>USD 6.00 / pack size not stated</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>Mechkeys</t>
+        </is>
+      </c>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>https://mechkeys.com/products/kailh-box-marshmallow-switches</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P156" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZIHXYTNKYf4</t>
@@ -11777,7 +12283,9 @@
       <c r="E157" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F157" s="2" t="n"/>
+      <c r="F157" s="2" t="n">
+        <v>75</v>
+      </c>
       <c r="G157" s="2" t="n">
         <v>60</v>
       </c>
@@ -11792,11 +12300,29 @@
           <t>loud, clicky</t>
         </is>
       </c>
-      <c r="K157" s="4" t="n"/>
-      <c r="L157" s="2" t="inlineStr"/>
-      <c r="M157" s="2" t="inlineStr"/>
-      <c r="N157" s="2" t="inlineStr"/>
-      <c r="O157" s="2" t="inlineStr"/>
+      <c r="K157" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.95 / 10 (pack size assumed 10, not stated)</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>Thock King</t>
+        </is>
+      </c>
+      <c r="N157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thockking.com/products/kailh-box-midnight-jade-clicky-switches</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P157" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7JbzW4-gbiY</t>
@@ -11813,7 +12339,11 @@
           <t>https://keeb-finder.com/switches/compare/kailh-box-fireflies-switches-vs-kailh-midnight-jade-switches</t>
         </is>
       </c>
-      <c r="T157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://www.thockking.com/products/kailh-box-midnight-jade-clicky-switches</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11843,7 +12373,9 @@
       <c r="G158" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="H158" s="3" t="n"/>
+      <c r="H158" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="I158" s="3" t="n">
         <v>3.6</v>
       </c>
@@ -11852,11 +12384,29 @@
           <t>silent, clicky</t>
         </is>
       </c>
-      <c r="K158" s="4" t="n"/>
-      <c r="L158" s="2" t="inlineStr"/>
-      <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr"/>
-      <c r="O158" s="2" t="inlineStr"/>
+      <c r="K158" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>USD 6.50 / 10</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N158" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/box-mute-jade</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P158" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FhmH7KwIw00</t>
@@ -11873,7 +12423,11 @@
           <t>https://milktooth.com/products/switches/box-mute-jade</t>
         </is>
       </c>
-      <c r="T158" s="2" t="inlineStr"/>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://milktooth.com/comparisons/box-mute-jade-vs-cj</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11910,11 +12464,29 @@
         <v>3.6</v>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="4" t="n"/>
-      <c r="L159" s="2" t="inlineStr"/>
-      <c r="M159" s="2" t="inlineStr"/>
-      <c r="N159" s="2" t="inlineStr"/>
-      <c r="O159" s="2" t="inlineStr"/>
+      <c r="K159" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.54 / 1 (DIYKEY, 10% off with KBDNEWS code)</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Box-Night-Firefly-163.html</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P159" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5V6BXatTJqg</t>
@@ -11957,7 +12529,9 @@
       <c r="E160" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="F160" s="2" t="n"/>
+      <c r="F160" s="2" t="n">
+        <v>75</v>
+      </c>
       <c r="G160" s="2" t="n">
         <v>70</v>
       </c>
@@ -11972,11 +12546,29 @@
           <t>audible</t>
         </is>
       </c>
-      <c r="K160" s="4" t="n"/>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr"/>
-      <c r="O160" s="2" t="inlineStr"/>
+      <c r="K160" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>CAD 105.99 / 110 (sold out; NovelKeys USD 18.00 / 36 also sold out)</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>Keychron Canada</t>
+        </is>
+      </c>
+      <c r="N160" s="5" t="inlineStr">
+        <is>
+          <t>https://keychron.ca/products/kailh-crystal-royal-box-tactile-switch</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P160" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tr8UqekYJ8w</t>
@@ -11993,7 +12585,11 @@
           <t>https://stackskb.com/store/novelkeys-x-kailh-box-royal, https://keygem.com/products/novelkeys-box-royal-switches-10-pack-retooled</t>
         </is>
       </c>
-      <c r="T160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://www.keychron.com/products/kailh-crystal-royal-box-tactile-switch</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -12034,11 +12630,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K161" s="4" t="n"/>
-      <c r="L161" s="2" t="inlineStr"/>
-      <c r="M161" s="2" t="inlineStr"/>
-      <c r="N161" s="2" t="inlineStr"/>
-      <c r="O161" s="2" t="inlineStr"/>
+      <c r="K161" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.50 / 10 (sold out)</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>Keyboardio</t>
+        </is>
+      </c>
+      <c r="N161" s="5" t="inlineStr">
+        <is>
+          <t>https://shop.keyboard.io/products/kailh-box-silent-pink-linear-switches-x-10</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P161" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6YruKmlgMgY</t>
@@ -12090,11 +12704,29 @@
         <v>4</v>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="4" t="n"/>
-      <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="2" t="inlineStr"/>
+      <c r="K162" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>USD 4.95 / 10</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>Thockking</t>
+        </is>
+      </c>
+      <c r="N162" s="5" t="inlineStr">
+        <is>
+          <t>https://thockking.com/products/kailh-box-strawberry-ice-cream-pro-linear-switches</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P162" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=gX4nfVYdEUg</t>
@@ -12146,11 +12778,29 @@
         <v>3.5</v>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
-      <c r="K163" s="4" t="n"/>
-      <c r="L163" s="2" t="inlineStr"/>
-      <c r="M163" s="2" t="inlineStr"/>
-      <c r="N163" s="2" t="inlineStr"/>
-      <c r="O163" s="2" t="inlineStr"/>
+      <c r="K163" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.59 / 1 (DIYKEY, after 10% KBDNEWS code; Chosfox USD 6.18 / 10 no code)</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N163" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-BOX-Taro-Ice-Cream-Pro-switch-162.html</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P163" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FBuKXsoUmgg</t>
@@ -12210,11 +12860,29 @@
           <t>crisp, clicky</t>
         </is>
       </c>
-      <c r="K164" s="4" t="n"/>
-      <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr"/>
-      <c r="O164" s="2" t="inlineStr"/>
+      <c r="K164" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.76 / 10</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N164" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/box-white</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P164" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hlCjITJI02Q</t>
@@ -12272,11 +12940,29 @@
           <t>clicky, crisp</t>
         </is>
       </c>
-      <c r="K165" s="4" t="n"/>
-      <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="2" t="inlineStr"/>
-      <c r="N165" s="2" t="inlineStr"/>
-      <c r="O165" s="2" t="inlineStr"/>
+      <c r="K165" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.00 / 10 (sale, reg 3.50; Divinikey USD 5.40 / 18 same per switch)</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N165" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/box-white-v2</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P165" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_aTBNp-fOgg</t>
@@ -12329,12 +13015,34 @@
       <c r="I166" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="4" t="n"/>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr"/>
-      <c r="O166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>medium sound level</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>CAD 44.99 / 45 (110-pack CAD 89.99 sold out)</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Keychron Canada</t>
+        </is>
+      </c>
+      <c r="N166" s="5" t="inlineStr">
+        <is>
+          <t>https://keychron.ca/products/kailh-box-winter-tactile-switch</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P166" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=RFcBLLQnzMI</t>
@@ -12380,7 +13088,9 @@
       <c r="F167" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="G167" s="2" t="n"/>
+      <c r="G167" s="2" t="n">
+        <v>55</v>
+      </c>
       <c r="H167" s="3" t="n">
         <v>1.3</v>
       </c>
@@ -12388,11 +13098,29 @@
         <v>3.2</v>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="4" t="n"/>
-      <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="inlineStr"/>
-      <c r="N167" s="2" t="inlineStr"/>
-      <c r="O167" s="2" t="inlineStr"/>
+      <c r="K167" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>GBP 0.95 / 10 = USD 0.13 / 1 per kbd.news (sold out)</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>Mechboards (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N167" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Choc-V2-Blue-397.html</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P167" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=d5VDNzgswCo</t>
@@ -12411,7 +13139,7 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>specs from maker site lookup</t>
+          <t>specs from maker site lookup; filled 2026-10-19 from https://kbd.news/switch/Kailh-Choc-V2-Blue-397.html</t>
         </is>
       </c>
     </row>
@@ -12442,7 +13170,9 @@
       <c r="F168" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="G168" s="2" t="n"/>
+      <c r="G168" s="2" t="n">
+        <v>80</v>
+      </c>
       <c r="H168" s="3" t="n">
         <v>1.3</v>
       </c>
@@ -12450,11 +13180,29 @@
         <v>3.2</v>
       </c>
       <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="4" t="n"/>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
-      <c r="N168" s="2" t="inlineStr"/>
-      <c r="O168" s="2" t="inlineStr"/>
+      <c r="K168" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.60 / 1 (Kailh store via kbd.news tracker; US 0.27 listing sold out)</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>Kailh store</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Choc-V2-Brown-456.html</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P168" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Z-jdEhT1Pn0</t>
@@ -12473,7 +13221,7 @@
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>force is third-party; the maker lists none; specs from maker site lookup</t>
+          <t>force is third-party; the maker lists none; specs from maker site lookup; filled 2026-10-19 from https://kbd.news/switch/Kailh-Choc-V2-Brown-456.html</t>
         </is>
       </c>
     </row>
@@ -12510,11 +13258,29 @@
         <v>3.2</v>
       </c>
       <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="4" t="n"/>
-      <c r="L169" s="2" t="inlineStr"/>
-      <c r="M169" s="2" t="inlineStr"/>
-      <c r="N169" s="2" t="inlineStr"/>
-      <c r="O169" s="2" t="inlineStr"/>
+      <c r="K169" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>USD 4.00 / 10 (sold out)</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>Keyboardio</t>
+        </is>
+      </c>
+      <c r="N169" s="5" t="inlineStr">
+        <is>
+          <t>https://shop.keyboard.io/products/kailh-choc-v2-red-linear-switches-x-10</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P169" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=VXPfzeLmQ5g</t>
@@ -12574,11 +13340,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K170" s="4" t="n"/>
-      <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
-      <c r="N170" s="2" t="inlineStr"/>
-      <c r="O170" s="2" t="inlineStr"/>
+      <c r="K170" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.52 / 1 (cheapest of several vendors, Pink Island)</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY/Kailh (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N170" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Deep-Sea-Silent-MINI-Pink-Island-274.html</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P170" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=SoTFWjQd1wI</t>
@@ -12638,11 +13422,29 @@
           <t>smooth, thocky, deep</t>
         </is>
       </c>
-      <c r="K171" s="4" t="n"/>
-      <c r="L171" s="2" t="inlineStr"/>
-      <c r="M171" s="2" t="inlineStr"/>
-      <c r="N171" s="2" t="inlineStr"/>
-      <c r="O171" s="2" t="inlineStr"/>
+      <c r="K171" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>USD 7.20 / 18</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>Divinikey</t>
+        </is>
+      </c>
+      <c r="N171" s="5" t="inlineStr">
+        <is>
+          <t>https://divinikey.com/products/kailh-folklore-wow-linear-switches</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P171" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hnbFc82L7v4</t>
@@ -12700,11 +13502,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K172" s="4" t="n"/>
-      <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr"/>
-      <c r="O172" s="2" t="inlineStr"/>
+      <c r="K172" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>FocusAttack</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr">
+        <is>
+          <t>https://focusattack.com/kailh-hide-mountain-clicky-full-pom-low-profile-mx-switch/</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P172" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uoWJBZEQ4C4</t>
@@ -12748,21 +13568,45 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n"/>
+      <c r="E173" s="2" t="n">
+        <v>45</v>
+      </c>
       <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
-      <c r="H173" s="3" t="n"/>
-      <c r="I173" s="3" t="n"/>
+      <c r="H173" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
           <t>hi-fi, smooth</t>
         </is>
       </c>
-      <c r="K173" s="4" t="n"/>
-      <c r="L173" s="2" t="inlineStr"/>
-      <c r="M173" s="2" t="inlineStr"/>
-      <c r="N173" s="2" t="inlineStr"/>
-      <c r="O173" s="2" t="inlineStr"/>
+      <c r="K173" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.77 / 1 (10% off with code KBDNEWS)</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N173" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Lunar-316.html</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P173" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ypb1npL4W4Y</t>
@@ -12775,7 +13619,11 @@
         </is>
       </c>
       <c r="S173" s="2" t="inlineStr"/>
-      <c r="T173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://kbd.news/switch/Kailh-Lunar-316.html</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -12818,11 +13666,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K174" s="4" t="n"/>
-      <c r="L174" s="2" t="inlineStr"/>
-      <c r="M174" s="2" t="inlineStr"/>
-      <c r="N174" s="2" t="inlineStr"/>
-      <c r="O174" s="2" t="inlineStr"/>
+      <c r="K174" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>USD 24.99 / 110 (sale, reg 29.99; set price across variants)</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N174" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/products/kailh-pro-switch</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P174" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=xy_YzGbIwfU</t>
@@ -12882,11 +13748,29 @@
           <t>quiet</t>
         </is>
       </c>
-      <c r="K175" s="4" t="n"/>
-      <c r="L175" s="2" t="inlineStr"/>
-      <c r="M175" s="2" t="inlineStr"/>
-      <c r="N175" s="2" t="inlineStr"/>
-      <c r="O175" s="2" t="inlineStr"/>
+      <c r="K175" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.28 / 1</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>KeebsForAll</t>
+        </is>
+      </c>
+      <c r="N175" s="5" t="inlineStr">
+        <is>
+          <t>https://keebsforall.com/products/kailh-pro-purple-switches</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P175" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=O4I5EHhzCyY</t>
@@ -12937,10 +13821,18 @@
         </is>
       </c>
       <c r="K176" s="4" t="n"/>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr"/>
-      <c r="O176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P176" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ktRBM-xsZ2E</t>
@@ -12980,7 +13872,9 @@
         <v>37</v>
       </c>
       <c r="F177" s="2" t="n"/>
-      <c r="G177" s="2" t="n"/>
+      <c r="G177" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="H177" s="3" t="n">
         <v>0.8</v>
       </c>
@@ -12988,11 +13882,29 @@
         <v>1.8</v>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="4" t="n"/>
-      <c r="L177" s="2" t="inlineStr"/>
-      <c r="M177" s="2" t="inlineStr"/>
-      <c r="N177" s="2" t="inlineStr"/>
-      <c r="O177" s="2" t="inlineStr"/>
+      <c r="K177" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.49 / 1 (Chosfox via kbd.news, Choc V2 version, may need KBDNEWS code)</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>Chosfox (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Saker-Mini-ChocV2-374.html</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P177" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=quicz1GqQZI</t>
@@ -13011,7 +13923,7 @@
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>specs from maker site lookup</t>
+          <t>specs from maker site lookup; filled 2026-10-19 from https://kbd.news/switch/Kailh-Saker-Mini-ChocV2-374.html</t>
         </is>
       </c>
     </row>
@@ -13052,11 +13964,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K178" s="4" t="n"/>
-      <c r="L178" s="2" t="inlineStr"/>
-      <c r="M178" s="2" t="inlineStr"/>
-      <c r="N178" s="2" t="inlineStr"/>
-      <c r="O178" s="2" t="inlineStr"/>
+      <c r="K178" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.54 / 1 (with KBDNEWS 10% code)</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>DIYKEY</t>
+        </is>
+      </c>
+      <c r="N178" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Silent-Latte-547.html</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P178" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=IFuJAqjgPw0</t>
@@ -13096,17 +14026,33 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n"/>
+      <c r="E179" s="2" t="n">
+        <v>42</v>
+      </c>
       <c r="F179" s="2" t="n"/>
-      <c r="G179" s="2" t="n"/>
-      <c r="H179" s="3" t="n"/>
-      <c r="I179" s="3" t="n"/>
+      <c r="G179" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="J179" s="2" t="inlineStr"/>
       <c r="K179" s="4" t="n"/>
-      <c r="L179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>no retail price found</t>
+        </is>
+      </c>
       <c r="M179" s="2" t="inlineStr"/>
       <c r="N179" s="2" t="inlineStr"/>
-      <c r="O179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P179" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=QEbxYIKRmWk</t>
@@ -13119,7 +14065,11 @@
         </is>
       </c>
       <c r="S179" s="2" t="inlineStr"/>
-      <c r="T179" s="2" t="inlineStr"/>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://www.globalsources.com/Keyboard-switch/Blue-Keyboard-Switch-1235883679p.htm</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -13145,7 +14095,9 @@
       <c r="E180" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F180" s="2" t="n"/>
+      <c r="F180" s="2" t="n">
+        <v>57</v>
+      </c>
       <c r="G180" s="2" t="n">
         <v>75</v>
       </c>
@@ -13160,11 +14112,29 @@
           <t>loud, clicky</t>
         </is>
       </c>
-      <c r="K180" s="4" t="n"/>
-      <c r="L180" s="2" t="inlineStr"/>
-      <c r="M180" s="2" t="inlineStr"/>
-      <c r="N180" s="2" t="inlineStr"/>
-      <c r="O180" s="2" t="inlineStr"/>
+      <c r="K180" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>USD 24.99 / 110 (set price across variants)</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N180" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/collections/keyboard-switch/products/kailh-speed-switch</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P180" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6FnC541qzMM</t>
@@ -13181,7 +14151,11 @@
           <t>https://www.kailh.net/products/kailh-speed-switch-set, https://novelkeys.com/products/kailh-switches</t>
         </is>
       </c>
-      <c r="T180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://www.rtings.com/keyboard-switch/tools/compare/kailh-box-white-kailh-speed-bronze/42710/42244</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -13224,11 +14198,29 @@
           <t>crisp</t>
         </is>
       </c>
-      <c r="K181" s="4" t="n"/>
-      <c r="L181" s="2" t="inlineStr"/>
-      <c r="M181" s="2" t="inlineStr"/>
-      <c r="N181" s="2" t="inlineStr"/>
-      <c r="O181" s="2" t="inlineStr"/>
+      <c r="K181" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>USD 24.99 / 110 (Kailh Speed set; copper colour not confirmed in listing)</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/collections/kailh-normal-profile-switches/products/kailh-speed-switch</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P181" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5Hkwzg09Woo</t>
@@ -13286,11 +14278,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K182" s="4" t="n"/>
-      <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="2" t="inlineStr"/>
-      <c r="N182" s="2" t="inlineStr"/>
-      <c r="O182" s="2" t="inlineStr"/>
+      <c r="K182" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>USD 24.99 / 110 (set)</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/collections/keyboard-switch/products/kailh-speed-switch</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P182" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=4_l_TmzBPZE</t>
@@ -13346,11 +14356,29 @@
           <t>creamy, smooth</t>
         </is>
       </c>
-      <c r="K183" s="4" t="n"/>
-      <c r="L183" s="2" t="inlineStr"/>
-      <c r="M183" s="2" t="inlineStr"/>
-      <c r="N183" s="2" t="inlineStr"/>
-      <c r="O183" s="2" t="inlineStr"/>
+      <c r="K183" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.46 / 1 (Chosfox via kbd.news, Choc V2 version; Focus Attack MX version USD 0.75 / 1)</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>Chosfox (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Spring-MINI-ChocV2-246.html</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P183" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=IjSGMiVLS7o</t>
@@ -13412,11 +14440,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K184" s="4" t="n"/>
-      <c r="L184" s="2" t="inlineStr"/>
-      <c r="M184" s="2" t="inlineStr"/>
-      <c r="N184" s="2" t="inlineStr"/>
-      <c r="O184" s="2" t="inlineStr"/>
+      <c r="K184" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>USD 15.96 / 35 (with KBDNEWS 5% code)</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>Chosfox</t>
+        </is>
+      </c>
+      <c r="N184" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Summer-Mini-switch-546.html</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P184" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Iik4_xE4kkM</t>
@@ -13466,7 +14512,9 @@
       <c r="F185" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G185" s="2" t="n"/>
+      <c r="G185" s="2" t="n">
+        <v>60</v>
+      </c>
       <c r="H185" s="3" t="n">
         <v>1.1</v>
       </c>
@@ -13474,11 +14522,29 @@
         <v>3.5</v>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
-      <c r="K185" s="4" t="n"/>
-      <c r="L185" s="2" t="inlineStr"/>
-      <c r="M185" s="2" t="inlineStr"/>
-      <c r="N185" s="2" t="inlineStr"/>
-      <c r="O185" s="2" t="inlineStr"/>
+      <c r="K185" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>USD 24.99 / 110</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/products/kailh-super-speed-switch</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P185" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0jWRLnTCX6w</t>
@@ -13495,7 +14561,11 @@
           <t>https://keychron.de/products/kailh-super-speed-switch</t>
         </is>
       </c>
-      <c r="T185" s="2" t="inlineStr"/>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://kbd.news/switch/Kailh-Super-Speed-Copper-377.html</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -13530,11 +14600,29 @@
         <v>3.5</v>
       </c>
       <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="4" t="n"/>
-      <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="inlineStr"/>
-      <c r="N186" s="2" t="inlineStr"/>
-      <c r="O186" s="2" t="inlineStr"/>
+      <c r="K186" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>USD 24.99 / 110 (another page shows 26.99)</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N186" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/collections/mechanical-switches/products/kailh-super-speed-switch</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P186" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=3Muaas-JG-g</t>
@@ -13586,11 +14674,29 @@
         <v>2.8</v>
       </c>
       <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="4" t="n"/>
-      <c r="L187" s="2" t="inlineStr"/>
-      <c r="M187" s="2" t="inlineStr"/>
-      <c r="N187" s="2" t="inlineStr"/>
-      <c r="O187" s="2" t="inlineStr"/>
+      <c r="K187" s="4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.53 / 1 (Chosfox, 110 pcs with 5% off; Focus Attack USD 0.75 / 1)</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>Chosfox (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N187" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Choc-V2-White-Rain-switch-231.html</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P187" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jN3TJzTU7m4</t>
@@ -13640,7 +14746,9 @@
       <c r="F188" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G188" s="2" t="n"/>
+      <c r="G188" s="2" t="n">
+        <v>52</v>
+      </c>
       <c r="H188" s="3" t="n">
         <v>1.2</v>
       </c>
@@ -13652,11 +14760,29 @@
           <t>creamy, smooth</t>
         </is>
       </c>
-      <c r="K188" s="4" t="n"/>
-      <c r="L188" s="2" t="inlineStr"/>
-      <c r="M188" s="2" t="inlineStr"/>
-      <c r="N188" s="2" t="inlineStr"/>
-      <c r="O188" s="2" t="inlineStr"/>
+      <c r="K188" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>USD 15.96 / 35</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>Chosfox (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N188" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Kailh-Winter-MINI-ChocV2-switch-247.html</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P188" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=F3h70TlYaIc</t>
@@ -13675,7 +14801,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>specs from maker site lookup</t>
+          <t>specs from maker site lookup; filled 2026-10-19 from https://www.rtings.com/keyboard-switch/reviews/kailh/winter-mini</t>
         </is>
       </c>
     </row>
@@ -13716,11 +14842,29 @@
           <t>quiet</t>
         </is>
       </c>
-      <c r="K189" s="4" t="n"/>
-      <c r="L189" s="2" t="inlineStr"/>
-      <c r="M189" s="2" t="inlineStr"/>
-      <c r="N189" s="2" t="inlineStr"/>
-      <c r="O189" s="2" t="inlineStr"/>
+      <c r="K189" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>USD 19.99 / 30 (USD 6.99 / 10)</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>MechKeys</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="inlineStr">
+        <is>
+          <t>https://mechkeys.com/products/kailh-newmen-indigo-naturalis-tactile-switches</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P189" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=yPzc3Xh5X7k</t>
@@ -13773,10 +14917,18 @@
         </is>
       </c>
       <c r="K190" s="4" t="n"/>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M190" s="2" t="inlineStr"/>
       <c r="N190" s="2" t="inlineStr"/>
-      <c r="O190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P190" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=RkksdfQo6XQ</t>
@@ -13834,11 +14986,29 @@
           <t>smooth</t>
         </is>
       </c>
-      <c r="K191" s="4" t="n"/>
-      <c r="L191" s="2" t="inlineStr"/>
-      <c r="M191" s="2" t="inlineStr"/>
-      <c r="N191" s="2" t="inlineStr"/>
-      <c r="O191" s="2" t="inlineStr"/>
+      <c r="K191" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>USD 12.50 / 35</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>KBDfans</t>
+        </is>
+      </c>
+      <c r="N191" s="5" t="inlineStr">
+        <is>
+          <t>https://kbdfans.com/products/kbdfans-roller-v2-linear-switches</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P191" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=orbFMbAVlhs</t>
@@ -13885,7 +15055,9 @@
       <c r="G192" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="H192" s="3" t="n"/>
+      <c r="H192" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I192" s="3" t="n">
         <v>3.6</v>
       </c>
@@ -13894,11 +15066,29 @@
           <t>smooth</t>
         </is>
       </c>
-      <c r="K192" s="4" t="n"/>
-      <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="2" t="inlineStr"/>
-      <c r="N192" s="2" t="inlineStr"/>
-      <c r="O192" s="2" t="inlineStr"/>
+      <c r="K192" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.76 / 18</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>Divinikey</t>
+        </is>
+      </c>
+      <c r="N192" s="5" t="inlineStr">
+        <is>
+          <t>https://divinikey.com/products/keygeek-y2-linear-switches</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P192" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GBWyqTLrWXM</t>
@@ -13915,7 +15105,11 @@
           <t>https://mekibo.com/products/keygeek-y2-linear-lubed-switches</t>
         </is>
       </c>
-      <c r="T192" s="2" t="inlineStr"/>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://divinikey.com/products/keygeek-y2-linear-switches</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -13945,10 +15139,18 @@
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="4" t="n"/>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M193" s="2" t="inlineStr"/>
       <c r="N193" s="2" t="inlineStr"/>
-      <c r="O193" s="2" t="inlineStr"/>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P193" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=z5l2ZezEUuA</t>
@@ -13991,7 +15193,9 @@
       <c r="G194" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="H194" s="3" t="n"/>
+      <c r="H194" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I194" s="3" t="n">
         <v>4</v>
       </c>
@@ -14000,11 +15204,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K194" s="4" t="n"/>
-      <c r="L194" s="2" t="inlineStr"/>
-      <c r="M194" s="2" t="inlineStr"/>
-      <c r="N194" s="2" t="inlineStr"/>
-      <c r="O194" s="2" t="inlineStr"/>
+      <c r="K194" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.55 / 10 (sale, MSRP 3.00; listed as Purple Click)</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N194" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/purple-click</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P194" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=cyMJPbftCF4</t>
@@ -14021,7 +15243,11 @@
           <t>https://milktooth.com/products/purple-click</t>
         </is>
       </c>
-      <c r="T194" s="2" t="inlineStr"/>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://milktooth.com/comparisons/mx-purple-rgb-vs-purple-click</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -14062,11 +15288,29 @@
           <t>clacky</t>
         </is>
       </c>
-      <c r="K195" s="4" t="n"/>
-      <c r="L195" s="2" t="inlineStr"/>
-      <c r="M195" s="2" t="inlineStr"/>
-      <c r="N195" s="2" t="inlineStr"/>
-      <c r="O195" s="2" t="inlineStr"/>
+      <c r="K195" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>USD 29.99 / 100</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>WhatGeek</t>
+        </is>
+      </c>
+      <c r="N195" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whatgeek.com/products/leobog-graywood-v4-linear-switches</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P195" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=f1csSojjpZk</t>
@@ -14124,11 +15368,29 @@
           <t>thocky</t>
         </is>
       </c>
-      <c r="K196" s="4" t="n"/>
-      <c r="L196" s="2" t="inlineStr"/>
-      <c r="M196" s="2" t="inlineStr"/>
-      <c r="N196" s="2" t="inlineStr"/>
-      <c r="O196" s="2" t="inlineStr"/>
+      <c r="K196" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.00 / 10</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>Ozo Keyboards</t>
+        </is>
+      </c>
+      <c r="N196" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ozokeyboards.com/products/leobog-ice-soul-tactile-switches</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P196" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=lxMxPBBUqLA</t>
@@ -14184,11 +15446,29 @@
           <t>smooth, thocky</t>
         </is>
       </c>
-      <c r="K197" s="4" t="n"/>
-      <c r="L197" s="2" t="inlineStr"/>
-      <c r="M197" s="2" t="inlineStr"/>
-      <c r="N197" s="2" t="inlineStr"/>
-      <c r="O197" s="2" t="inlineStr"/>
+      <c r="K197" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>USD 26.99 / 100 (pack size inferred; listing no longer in Epomaker search)</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>Epomaker</t>
+        </is>
+      </c>
+      <c r="N197" s="5" t="inlineStr">
+        <is>
+          <t>https://epomaker.com/products/leobog-ink-crystal-switch-v3</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P197" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=1dCKmF3bW7g</t>
@@ -14296,11 +15576,29 @@
           <t>smooth</t>
         </is>
       </c>
-      <c r="K199" s="4" t="n"/>
-      <c r="L199" s="2" t="inlineStr"/>
-      <c r="M199" s="2" t="inlineStr"/>
-      <c r="N199" s="2" t="inlineStr"/>
-      <c r="O199" s="2" t="inlineStr"/>
+      <c r="K199" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>USD 12.99 / 35</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>Epomaker</t>
+        </is>
+      </c>
+      <c r="N199" s="5" t="inlineStr">
+        <is>
+          <t>https://epomaker.com/products/leobog-nimbus-switch-v3</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P199" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GIgtQwJiBBo</t>
@@ -14358,11 +15656,29 @@
           <t>creamy</t>
         </is>
       </c>
-      <c r="K200" s="4" t="n"/>
-      <c r="L200" s="2" t="inlineStr"/>
-      <c r="M200" s="2" t="inlineStr"/>
-      <c r="N200" s="2" t="inlineStr"/>
-      <c r="O200" s="2" t="inlineStr"/>
+      <c r="K200" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>USD 26.99 / 100</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>Epomaker</t>
+        </is>
+      </c>
+      <c r="N200" s="5" t="inlineStr">
+        <is>
+          <t>https://epomaker.com/products/leobog-reaper-switch-set</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P200" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=nnRa7OGj72c</t>
@@ -14414,11 +15730,29 @@
         <v>2.8</v>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="4" t="n"/>
-      <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="2" t="inlineStr"/>
-      <c r="N201" s="2" t="inlineStr"/>
-      <c r="O201" s="2" t="inlineStr"/>
+      <c r="K201" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>USD 59.00 / 90 (sale; listing also says 106 pcs, 90 used; Focus Attack Kailh Ghost USD 0.95 / 1)</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>Lofree</t>
+        </is>
+      </c>
+      <c r="N201" s="5" t="inlineStr">
+        <is>
+          <t>https://lofree.co/products/lofree-ghost-switches</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P201" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=VBFy1o1ndCw</t>
@@ -14478,11 +15812,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K202" s="4" t="n"/>
-      <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="inlineStr"/>
-      <c r="N202" s="2" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr"/>
+      <c r="K202" s="4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>USD 59.00 / 106</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>Lofree</t>
+        </is>
+      </c>
+      <c r="N202" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lofree.co/products/hades-low-profile-pom-switches</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P202" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_SQMcMd2R54</t>
@@ -14540,11 +15892,29 @@
         <v>2.8</v>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
-      <c r="K203" s="4" t="n"/>
-      <c r="L203" s="2" t="inlineStr"/>
-      <c r="M203" s="2" t="inlineStr"/>
-      <c r="N203" s="2" t="inlineStr"/>
-      <c r="O203" s="2" t="inlineStr"/>
+      <c r="K203" s="4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>USD 59.00 / 106</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>Lofree</t>
+        </is>
+      </c>
+      <c r="N203" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lofree.co/products/lofree-phantom-switches</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P203" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=wG2-PQ1EpsI</t>
@@ -14600,11 +15970,29 @@
         <v>2.8</v>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="4" t="n"/>
-      <c r="L204" s="2" t="inlineStr"/>
-      <c r="M204" s="2" t="inlineStr"/>
-      <c r="N204" s="2" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr"/>
+      <c r="K204" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>USD 60.00 / 106 (Amazon third-party, Dec 2025)</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="N204" s="5" t="inlineStr">
+        <is>
+          <t>https://camelcamelcamel.com/product/B0F5BTB3SN</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P204" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jFr4unXH4lY</t>
@@ -14667,10 +16055,18 @@
         </is>
       </c>
       <c r="K205" s="4" t="n"/>
-      <c r="L205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M205" s="2" t="inlineStr"/>
       <c r="N205" s="2" t="inlineStr"/>
-      <c r="O205" s="2" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P205" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GoJhD_PZvZ4</t>
@@ -14730,11 +16126,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K206" s="4" t="n"/>
-      <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="2" t="inlineStr"/>
-      <c r="N206" s="2" t="inlineStr"/>
-      <c r="O206" s="2" t="inlineStr"/>
+      <c r="K206" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.75 / 1 (Matias Standard 60g Clicky, unit unclear)</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>MechanicalKeyboards.com</t>
+        </is>
+      </c>
+      <c r="N206" s="5" t="inlineStr">
+        <is>
+          <t>https://mechanicalkeyboards.com/collections/matias-switches</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P206" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Y_y9D6cTews</t>
@@ -14790,11 +16204,29 @@
           <t>quiet</t>
         </is>
       </c>
-      <c r="K207" s="4" t="n"/>
-      <c r="L207" s="2" t="inlineStr"/>
-      <c r="M207" s="2" t="inlineStr"/>
-      <c r="N207" s="2" t="inlineStr"/>
-      <c r="O207" s="2" t="inlineStr"/>
+      <c r="K207" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>MechanicalKeyboards.com</t>
+        </is>
+      </c>
+      <c r="N207" s="5" t="inlineStr">
+        <is>
+          <t>https://mechanicalkeyboards.com/collections/matias-switches</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P207" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ILAm3Pexf_o</t>
@@ -14850,11 +16282,29 @@
           <t>quiet</t>
         </is>
       </c>
-      <c r="K208" s="4" t="n"/>
-      <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr"/>
-      <c r="N208" s="2" t="inlineStr"/>
-      <c r="O208" s="2" t="inlineStr"/>
+      <c r="K208" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>MechanicalKeyboards.com</t>
+        </is>
+      </c>
+      <c r="N208" s="5" t="inlineStr">
+        <is>
+          <t>https://mechanicalkeyboards.com/products/matias-quiet-linear-35g-switch</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P208" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=H2ID8HG21OE</t>
@@ -14912,11 +16362,29 @@
           <t>loud</t>
         </is>
       </c>
-      <c r="K209" s="4" t="n"/>
-      <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="2" t="inlineStr"/>
-      <c r="N209" s="2" t="inlineStr"/>
-      <c r="O209" s="2" t="inlineStr"/>
+      <c r="K209" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.60 / 10</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>UniKeys</t>
+        </is>
+      </c>
+      <c r="N209" s="5" t="inlineStr">
+        <is>
+          <t>https://unikeyboards.com/products/mdd-princess-linear-switch-factory-lubed-edition-10pcs</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P209" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FIbnLwSNbMU</t>
@@ -14970,11 +16438,29 @@
         <v>3.2</v>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="4" t="n"/>
-      <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="2" t="inlineStr"/>
-      <c r="O210" s="2" t="inlineStr"/>
+      <c r="K210" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>USD 1.80 / 10 (sale, reg 2.00)</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>KBDfans</t>
+        </is>
+      </c>
+      <c r="N210" s="5" t="inlineStr">
+        <is>
+          <t>https://kbdfans.com/products/mmd-princess-linear-tactile-switches-v2</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P210" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=htESGay9biE</t>
@@ -15032,11 +16518,29 @@
           <t>loud</t>
         </is>
       </c>
-      <c r="K211" s="4" t="n"/>
-      <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr"/>
-      <c r="N211" s="2" t="inlineStr"/>
-      <c r="O211" s="2" t="inlineStr"/>
+      <c r="K211" s="4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.33 / 1</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>MaxGaming US</t>
+        </is>
+      </c>
+      <c r="N211" s="5" t="inlineStr">
+        <is>
+          <t>https://us.maxgaming.com/us/switches/princess-v3-tactile-switch</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P211" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tv1Vg2fQjI4</t>
@@ -15084,7 +16588,9 @@
         <v>58</v>
       </c>
       <c r="F212" s="2" t="n"/>
-      <c r="G212" s="2" t="n"/>
+      <c r="G212" s="2" t="n">
+        <v>58</v>
+      </c>
       <c r="H212" s="3" t="n">
         <v>2</v>
       </c>
@@ -15097,10 +16603,26 @@
         </is>
       </c>
       <c r="K212" s="4" t="n"/>
-      <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="2" t="inlineStr"/>
-      <c r="N212" s="2" t="inlineStr"/>
-      <c r="O212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>GBP 3.00 / 10 (sale; GBP only, not converted)</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>The Thocc Exchange</t>
+        </is>
+      </c>
+      <c r="N212" s="5" t="inlineStr">
+        <is>
+          <t>https://thoccexchange.com/products/moyu-studio-fuyu-linear-switches-10-pack</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P212" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=8qiac2-DYtA</t>
@@ -15117,7 +16639,11 @@
           <t>https://thoccexchange.com/products/moyu-studio-fuyu-linear-switches-10-pack</t>
         </is>
       </c>
-      <c r="T212" s="2" t="inlineStr"/>
+      <c r="T212" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://keeb-finder.com/switches/compare/cherry-mx-speed-silver-45g-linear-vs-moyu-studio-fuyu-linear-switches-10-pack</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -15147,10 +16673,18 @@
       <c r="I213" s="3" t="n"/>
       <c r="J213" s="2" t="inlineStr"/>
       <c r="K213" s="4" t="n"/>
-      <c r="L213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M213" s="2" t="inlineStr"/>
       <c r="N213" s="2" t="inlineStr"/>
-      <c r="O213" s="2" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P213" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=s1j7mbebKb4</t>
@@ -15197,10 +16731,18 @@
       <c r="I214" s="3" t="n"/>
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="4" t="n"/>
-      <c r="L214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>not found (no clicky Cream variant located)</t>
+        </is>
+      </c>
       <c r="M214" s="2" t="inlineStr"/>
       <c r="N214" s="2" t="inlineStr"/>
-      <c r="O214" s="2" t="inlineStr"/>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P214" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=fKoLt26B_AY</t>
@@ -15256,11 +16798,29 @@
           <t>loud, clicky</t>
         </is>
       </c>
-      <c r="K215" s="4" t="n"/>
-      <c r="L215" s="2" t="inlineStr"/>
-      <c r="M215" s="2" t="inlineStr"/>
-      <c r="N215" s="2" t="inlineStr"/>
-      <c r="O215" s="2" t="inlineStr"/>
+      <c r="K215" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>CAD 54.99 / 110 (sold out; Kailh-branded set)</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>Keychron Canada</t>
+        </is>
+      </c>
+      <c r="N215" s="5" t="inlineStr">
+        <is>
+          <t>https://keychron.ca/products/kailh-box-switch-set</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P215" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=VMKZcNaBGFs</t>
@@ -15320,11 +16880,29 @@
           <t>loud, clicky</t>
         </is>
       </c>
-      <c r="K216" s="4" t="n"/>
-      <c r="L216" s="2" t="inlineStr"/>
-      <c r="M216" s="2" t="inlineStr"/>
-      <c r="N216" s="2" t="inlineStr"/>
-      <c r="O216" s="2" t="inlineStr"/>
+      <c r="K216" s="4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>USD 6.30 / 18 (sold out)</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>Divinikey</t>
+        </is>
+      </c>
+      <c r="N216" s="5" t="inlineStr">
+        <is>
+          <t>https://divinikey.com/collections/switches/products/kailh-box-navy-clicky-switches</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P216" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hrF6grCBLIQ</t>
@@ -15384,11 +16962,29 @@
           <t>clicky, crisp</t>
         </is>
       </c>
-      <c r="K217" s="4" t="n"/>
-      <c r="L217" s="2" t="inlineStr"/>
-      <c r="M217" s="2" t="inlineStr"/>
-      <c r="N217" s="2" t="inlineStr"/>
-      <c r="O217" s="2" t="inlineStr"/>
+      <c r="K217" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>USD 44.99 / 110 (Keychron Kailh BOX Heavy Pale Blue set)</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>Keychron</t>
+        </is>
+      </c>
+      <c r="N217" s="5" t="inlineStr">
+        <is>
+          <t>https://www.keychron.com/collections/add-on-for-v8-plates/products/kailh-box-heavy-switch</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P217" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=MXLYrjawyq8</t>
@@ -15448,11 +17044,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K218" s="4" t="n"/>
-      <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="2" t="inlineStr"/>
-      <c r="N218" s="2" t="inlineStr"/>
-      <c r="O218" s="2" t="inlineStr"/>
+      <c r="K218" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.95 / 10 (Divinikey NK version USD 3.40 / 10 sold out)</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>Thock King</t>
+        </is>
+      </c>
+      <c r="N218" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thockking.com/collections/all/products/kailh-box-pink-clicky-switches</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P218" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Rhu7n5HabKs</t>
@@ -15512,11 +17126,29 @@
           <t>creamy</t>
         </is>
       </c>
-      <c r="K219" s="4" t="n"/>
-      <c r="L219" s="2" t="inlineStr"/>
-      <c r="M219" s="2" t="inlineStr"/>
-      <c r="N219" s="2" t="inlineStr"/>
-      <c r="O219" s="2" t="inlineStr"/>
+      <c r="K219" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>USD 6.25 / 10 (MSRP 6.50)</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N219" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/novelkeys-blueberry</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P219" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uw6irg5qiAU</t>
@@ -15576,11 +17208,29 @@
           <t>loud</t>
         </is>
       </c>
-      <c r="K220" s="4" t="n"/>
-      <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="2" t="inlineStr"/>
-      <c r="N220" s="2" t="inlineStr"/>
-      <c r="O220" s="2" t="inlineStr"/>
+      <c r="K220" s="4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>USD 16.20 / 36 (sold out)</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>NovelKeys</t>
+        </is>
+      </c>
+      <c r="N220" s="5" t="inlineStr">
+        <is>
+          <t>https://novelkeys.com/products/kailh-switches</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P220" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=IHAJcSY7nY0</t>
@@ -15638,11 +17288,29 @@
           <t>clicky</t>
         </is>
       </c>
-      <c r="K221" s="4" t="n"/>
-      <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="2" t="inlineStr"/>
-      <c r="N221" s="2" t="inlineStr"/>
-      <c r="O221" s="2" t="inlineStr"/>
+      <c r="K221" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10 (out of stock)</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N221" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/outemu-cream-blue</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P221" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=xTa7TOTBT1g</t>
@@ -15700,11 +17368,29 @@
           <t>creamy</t>
         </is>
       </c>
-      <c r="K222" s="4" t="n"/>
-      <c r="L222" s="2" t="inlineStr"/>
-      <c r="M222" s="2" t="inlineStr"/>
-      <c r="N222" s="2" t="inlineStr"/>
-      <c r="O222" s="2" t="inlineStr"/>
+      <c r="K222" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N222" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/outemu-cream-pink-vs-outemu-peach</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P222" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NoQbC_F2NiE</t>
@@ -15762,11 +17448,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K223" s="4" t="n"/>
-      <c r="L223" s="2" t="inlineStr"/>
-      <c r="M223" s="2" t="inlineStr"/>
-      <c r="N223" s="2" t="inlineStr"/>
-      <c r="O223" s="2" t="inlineStr"/>
+      <c r="K223" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N223" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/outemu-cream-yellow-vs-yellow-silver</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P223" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZjWb0XJOXV4</t>
@@ -15820,11 +17524,29 @@
         <v>4</v>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="4" t="n"/>
-      <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="inlineStr"/>
-      <c r="N224" s="2" t="inlineStr"/>
-      <c r="O224" s="2" t="inlineStr"/>
+      <c r="K224" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N224" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/outemu-dustproof-black-vs-snow</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P224" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=j1zXI_7e90o</t>
@@ -15876,11 +17598,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K225" s="4" t="n"/>
-      <c r="L225" s="2" t="inlineStr"/>
-      <c r="M225" s="2" t="inlineStr"/>
-      <c r="N225" s="2" t="inlineStr"/>
-      <c r="O225" s="2" t="inlineStr"/>
+      <c r="K225" s="4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.50 / 10 (factory lubed)</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>Lumekeebs</t>
+        </is>
+      </c>
+      <c r="N225" s="5" t="inlineStr">
+        <is>
+          <t>https://lumekeebs.com/products/outemu-green-banana-silent-tactile-switches</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P225" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZwvCdBLz2eI</t>
@@ -15940,11 +17680,29 @@
           <t>creamy</t>
         </is>
       </c>
-      <c r="K226" s="4" t="n"/>
-      <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="2" t="inlineStr"/>
-      <c r="N226" s="2" t="inlineStr"/>
-      <c r="O226" s="2" t="inlineStr"/>
+      <c r="K226" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10 (sold out)</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N226" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/outemu-maple-leaf</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P226" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oj7MptgLmWw</t>
@@ -15984,21 +17742,47 @@
           <t>Alps/other</t>
         </is>
       </c>
-      <c r="E227" s="2" t="n"/>
+      <c r="E227" s="2" t="n">
+        <v>46</v>
+      </c>
       <c r="F227" s="2" t="n"/>
-      <c r="G227" s="2" t="n"/>
-      <c r="H227" s="3" t="n"/>
-      <c r="I227" s="3" t="n"/>
+      <c r="G227" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
           <t>smooth</t>
         </is>
       </c>
-      <c r="K227" s="4" t="n"/>
-      <c r="L227" s="2" t="inlineStr"/>
-      <c r="M227" s="2" t="inlineStr"/>
-      <c r="N227" s="2" t="inlineStr"/>
-      <c r="O227" s="2" t="inlineStr"/>
+      <c r="K227" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10 (Outemu Red listing; out of stock)</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N227" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/outemu-red</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P227" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0RjSajLHhKY</t>
@@ -16011,7 +17795,11 @@
         </is>
       </c>
       <c r="S227" s="2" t="inlineStr"/>
-      <c r="T227" s="2" t="inlineStr"/>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://milktooth.com/products/outemu-red https://comparigon.com/keyboard-switches/outemu-dustproof-red</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -16110,11 +17898,29 @@
           <t>smooth, loud</t>
         </is>
       </c>
-      <c r="K229" s="4" t="n"/>
-      <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="inlineStr"/>
-      <c r="N229" s="2" t="inlineStr"/>
-      <c r="O229" s="2" t="inlineStr"/>
+      <c r="K229" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N229" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/switches/pear</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P229" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=SGroxiWb6Y8</t>
@@ -16157,7 +17963,9 @@
       <c r="E230" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="F230" s="2" t="n"/>
+      <c r="F230" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="G230" s="2" t="n">
         <v>50</v>
       </c>
@@ -16172,11 +17980,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K230" s="4" t="n"/>
-      <c r="L230" s="2" t="inlineStr"/>
-      <c r="M230" s="2" t="inlineStr"/>
-      <c r="N230" s="2" t="inlineStr"/>
-      <c r="O230" s="2" t="inlineStr"/>
+      <c r="K230" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.20 / 10 (listing ambiguous)</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>Thock King</t>
+        </is>
+      </c>
+      <c r="N230" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thockking.com/products/ttc-gold-pink-v2-linear-switches-copy</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P230" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=OaeDDEU5CAQ</t>
@@ -16193,7 +18019,11 @@
           <t>https://lumekeebs.com/en-de/products/outemu-silent-lemon-tactile-v2-switches</t>
         </is>
       </c>
-      <c r="T230" s="2" t="inlineStr"/>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://comparigon.com/keyboard-switches/outemu-silent-lemon-v2</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -16230,11 +18060,29 @@
         <v>3.3</v>
       </c>
       <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="4" t="n"/>
-      <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
-      <c r="N231" s="2" t="inlineStr"/>
-      <c r="O231" s="2" t="inlineStr"/>
+      <c r="K231" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.20 / 10 (pack size assumed; kbd.news shops ~USD 0.21 / 1 with coupon)</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>Thock King</t>
+        </is>
+      </c>
+      <c r="N231" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thockking.com/products/outemu-silent-lemon-tactile-v3-switches</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P231" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AOBsX07cp1c</t>
@@ -16292,11 +18140,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K232" s="4" t="n"/>
-      <c r="L232" s="2" t="inlineStr"/>
-      <c r="M232" s="2" t="inlineStr"/>
-      <c r="N232" s="2" t="inlineStr"/>
-      <c r="O232" s="2" t="inlineStr"/>
+      <c r="K232" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10 (sold out)</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N232" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/outemu-silent-ocean</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P232" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qeBJMEgDYGU</t>
@@ -16336,21 +18202,37 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E233" s="2" t="n"/>
+      <c r="E233" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="F233" s="2" t="n"/>
-      <c r="G233" s="2" t="n"/>
-      <c r="H233" s="3" t="n"/>
-      <c r="I233" s="3" t="n"/>
+      <c r="G233" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H233" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I233" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
           <t>silent</t>
         </is>
       </c>
       <c r="K233" s="4" t="n"/>
-      <c r="L233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>no price found (V3 is what retailers stock)</t>
+        </is>
+      </c>
       <c r="M233" s="2" t="inlineStr"/>
       <c r="N233" s="2" t="inlineStr"/>
-      <c r="O233" s="2" t="inlineStr"/>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P233" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=1cwO4usiVvQ</t>
@@ -16363,7 +18245,11 @@
         </is>
       </c>
       <c r="S233" s="2" t="inlineStr"/>
-      <c r="T233" s="2" t="inlineStr"/>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://comparigon.com/keyboard-switches/outemu-silent-peach-v2</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -16390,7 +18276,9 @@
         <v>40</v>
       </c>
       <c r="F234" s="2" t="n"/>
-      <c r="G234" s="2" t="n"/>
+      <c r="G234" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="H234" s="3" t="n">
         <v>2</v>
       </c>
@@ -16398,11 +18286,29 @@
         <v>3.3</v>
       </c>
       <c r="J234" s="2" t="inlineStr"/>
-      <c r="K234" s="4" t="n"/>
-      <c r="L234" s="2" t="inlineStr"/>
-      <c r="M234" s="2" t="inlineStr"/>
-      <c r="N234" s="2" t="inlineStr"/>
-      <c r="O234" s="2" t="inlineStr"/>
+      <c r="K234" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.40 / 18</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>Divinikey</t>
+        </is>
+      </c>
+      <c r="N234" s="5" t="inlineStr">
+        <is>
+          <t>https://divinikey.com/products/outemu-silent-peach-v3-linear-switches</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P234" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=IvxGnt47JFE</t>
@@ -16419,7 +18325,11 @@
           <t>https://divinikey.com/products/outemu-silent-peach-v3-linear-switches</t>
         </is>
       </c>
-      <c r="T234" s="2" t="inlineStr"/>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://kbd.news/switch/Outemu-Silent-Peach-V3-190.html</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -16462,11 +18372,29 @@
           <t>quiet, muted, thocky</t>
         </is>
       </c>
-      <c r="K235" s="4" t="n"/>
-      <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="2" t="inlineStr"/>
-      <c r="N235" s="2" t="inlineStr"/>
-      <c r="O235" s="2" t="inlineStr"/>
+      <c r="K235" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N235" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/outemu-silent-yellow-jade-vs-yellow-silver</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P235" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-4jMKjtt4ZY</t>
@@ -16521,12 +18449,34 @@
       <c r="I236" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="4" t="n"/>
-      <c r="L236" s="2" t="inlineStr"/>
-      <c r="M236" s="2" t="inlineStr"/>
-      <c r="N236" s="2" t="inlineStr"/>
-      <c r="O236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>clicky</t>
+        </is>
+      </c>
+      <c r="K236" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.10 / 10</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N236" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/outemu-spring-breeze-vs-tomcat</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P236" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hQd5MNTdICA</t>
@@ -16575,10 +18525,18 @@
       <c r="I237" s="3" t="n"/>
       <c r="J237" s="2" t="inlineStr"/>
       <c r="K237" s="4" t="n"/>
-      <c r="L237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>not sold (vintage, no retail listing)</t>
+        </is>
+      </c>
       <c r="M237" s="2" t="inlineStr"/>
       <c r="N237" s="2" t="inlineStr"/>
-      <c r="O237" s="2" t="inlineStr"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P237" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=pZzPoGghXdQ</t>
@@ -16632,11 +18590,29 @@
         <v>3.3</v>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="4" t="n"/>
-      <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="2" t="inlineStr"/>
-      <c r="N238" s="2" t="inlineStr"/>
-      <c r="O238" s="2" t="inlineStr"/>
+      <c r="K238" s="4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>USD 13.99 / 24 (sold out; open-box listing USD 7.99)</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>Redragon store</t>
+        </is>
+      </c>
+      <c r="N238" s="5" t="inlineStr">
+        <is>
+          <t>https://redragonshop.com/products/a113f-mechanical-switch</t>
+        </is>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P238" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vMIJzM-JQsQ</t>
@@ -16694,11 +18670,29 @@
           <t>quiet</t>
         </is>
       </c>
-      <c r="K239" s="4" t="n"/>
-      <c r="L239" s="2" t="inlineStr"/>
-      <c r="M239" s="2" t="inlineStr"/>
-      <c r="N239" s="2" t="inlineStr"/>
-      <c r="O239" s="2" t="inlineStr"/>
+      <c r="K239" s="4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>USD 11.99 / 70 (sale from 19.99; sold out)</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr">
+        <is>
+          <t>Redragon (official)</t>
+        </is>
+      </c>
+      <c r="N239" s="5" t="inlineStr">
+        <is>
+          <t>https://redragonshop.com/products/redragon-bean-a120-soft-linear-mechanical-switch</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P239" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=K5IU8gVpjGg</t>
@@ -16756,11 +18750,29 @@
           <t>silent, quiet</t>
         </is>
       </c>
-      <c r="K240" s="4" t="n"/>
-      <c r="L240" s="2" t="inlineStr"/>
-      <c r="M240" s="2" t="inlineStr"/>
-      <c r="N240" s="2" t="inlineStr"/>
-      <c r="O240" s="2" t="inlineStr"/>
+      <c r="K240" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>USD 19.99 / 70 (regular; sale 15.99 / 70 seen; some pages sold out)</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>Redragon store</t>
+        </is>
+      </c>
+      <c r="N240" s="5" t="inlineStr">
+        <is>
+          <t>https://redragonshop.com/products/redragon-stars-a120-silent-tactile-mechanical-switch</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P240" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=OCz6ZMBCHnU</t>
@@ -16819,10 +18831,18 @@
         </is>
       </c>
       <c r="K241" s="4" t="n"/>
-      <c r="L241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="M241" s="2" t="inlineStr"/>
       <c r="N241" s="2" t="inlineStr"/>
-      <c r="O241" s="2" t="inlineStr"/>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P241" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=SyV6_FQ_gFU</t>
@@ -16880,11 +18900,29 @@
           <t>clacky</t>
         </is>
       </c>
-      <c r="K242" s="4" t="n"/>
-      <c r="L242" s="2" t="inlineStr"/>
-      <c r="M242" s="2" t="inlineStr"/>
-      <c r="N242" s="2" t="inlineStr"/>
-      <c r="O242" s="2" t="inlineStr"/>
+      <c r="K242" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>USD 7.74 / 18 (0.43 each, sold out)</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>Divinikey</t>
+        </is>
+      </c>
+      <c r="N242" s="5" t="inlineStr">
+        <is>
+          <t>https://divinikey.com/products/tecsee-purple-panda-tactile-switches</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P242" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7PzMRX3KGgI</t>
@@ -16930,7 +18968,9 @@
       <c r="F243" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="G243" s="2" t="n"/>
+      <c r="G243" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="H243" s="3" t="n">
         <v>2</v>
       </c>
@@ -16938,11 +18978,29 @@
         <v>3.5</v>
       </c>
       <c r="J243" s="2" t="inlineStr"/>
-      <c r="K243" s="4" t="n"/>
-      <c r="L243" s="2" t="inlineStr"/>
-      <c r="M243" s="2" t="inlineStr"/>
-      <c r="N243" s="2" t="inlineStr"/>
-      <c r="O243" s="2" t="inlineStr"/>
+      <c r="K243" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>USD 6.60 / 10 (MSRP)</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N243" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/bluish-white-vs-type-s</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P243" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=TrzocDhDTbk</t>
@@ -16959,7 +19017,11 @@
           <t>https://kbd.news/switch/TTC-Bluish-White-491.html</t>
         </is>
       </c>
-      <c r="T243" s="2" t="inlineStr"/>
+      <c r="T243" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://milktooth.com/comparisons/bluish-white-vs-type-s</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -16996,11 +19058,29 @@
           <t>smooth</t>
         </is>
       </c>
-      <c r="K244" s="4" t="n"/>
-      <c r="L244" s="2" t="inlineStr"/>
-      <c r="M244" s="2" t="inlineStr"/>
-      <c r="N244" s="2" t="inlineStr"/>
-      <c r="O244" s="2" t="inlineStr"/>
+      <c r="K244" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>CAD 7.50 / 10</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>BeaverKeys</t>
+        </is>
+      </c>
+      <c r="N244" s="5" t="inlineStr">
+        <is>
+          <t>https://beaverkeys.ca/products/ttc-elf-king-he</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P244" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=2VqIP2ZmsQc</t>
@@ -17057,12 +19137,34 @@
       <c r="I245" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J245" s="2" t="inlineStr"/>
-      <c r="K245" s="4" t="n"/>
-      <c r="L245" s="2" t="inlineStr"/>
-      <c r="M245" s="2" t="inlineStr"/>
-      <c r="N245" s="2" t="inlineStr"/>
-      <c r="O245" s="2" t="inlineStr"/>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>bassy, low-pitched, poppy, resonant</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>USD 4.30 / 10 (sale from 8.30; out of stock)</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N245" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/flaming-purple</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P245" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=9Aa5HNhkMHw</t>
@@ -17106,7 +19208,9 @@
         <v>39</v>
       </c>
       <c r="F246" s="2" t="n"/>
-      <c r="G246" s="2" t="n"/>
+      <c r="G246" s="2" t="n">
+        <v>43</v>
+      </c>
       <c r="H246" s="3" t="n">
         <v>2</v>
       </c>
@@ -17118,11 +19222,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K246" s="4" t="n"/>
-      <c r="L246" s="2" t="inlineStr"/>
-      <c r="M246" s="2" t="inlineStr"/>
-      <c r="N246" s="2" t="inlineStr"/>
-      <c r="O246" s="2" t="inlineStr"/>
+      <c r="K246" s="4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.55 / 10 (sale, MSRP 8.61)</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N246" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/switches/silent-frozen</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P246" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uBbzqunNFsI</t>
@@ -17139,7 +19261,11 @@
           <t>https://chosfox.com/products/ttc-frozen-silent-v2-switch</t>
         </is>
       </c>
-      <c r="T246" s="2" t="inlineStr"/>
+      <c r="T246" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://milktooth.com/products/switches/silent-frozen</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -17170,11 +19296,29 @@
         <v>3.4</v>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
-      <c r="K247" s="4" t="n"/>
-      <c r="L247" s="2" t="inlineStr"/>
-      <c r="M247" s="2" t="inlineStr"/>
-      <c r="N247" s="2" t="inlineStr"/>
-      <c r="O247" s="2" t="inlineStr"/>
+      <c r="K247" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>USD 14.75 / 15 (TTCswitch, after 5% KBDNEWS code)</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>TTCswitch (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N247" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/TTC-Pro-KOM-HE-Magneto-542.html</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P247" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=W6B520Bf2UQ</t>
@@ -17232,11 +19376,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K248" s="4" t="n"/>
-      <c r="L248" s="2" t="inlineStr"/>
-      <c r="M248" s="2" t="inlineStr"/>
-      <c r="N248" s="2" t="inlineStr"/>
-      <c r="O248" s="2" t="inlineStr"/>
+      <c r="K248" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.35 / 10 (sale, was 6.60)</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N248" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/products/silent-bluish-white</t>
+        </is>
+      </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P248" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FpnooDggOk4</t>
@@ -17288,11 +19450,29 @@
         <v>3.4</v>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
-      <c r="K249" s="4" t="n"/>
-      <c r="L249" s="2" t="inlineStr"/>
-      <c r="M249" s="2" t="inlineStr"/>
-      <c r="N249" s="2" t="inlineStr"/>
-      <c r="O249" s="2" t="inlineStr"/>
+      <c r="K249" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>USD 8.99 / 10</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Power store</t>
+        </is>
+      </c>
+      <c r="N249" s="5" t="inlineStr">
+        <is>
+          <t>https://sp-siliconpower.com/products/ttc-speed-silver-v2-switches</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P249" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=THZ6AFr6ucQ</t>
@@ -17342,11 +19522,29 @@
         <v>3.4</v>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
-      <c r="K250" s="4" t="n"/>
-      <c r="L250" s="2" t="inlineStr"/>
-      <c r="M250" s="2" t="inlineStr"/>
-      <c r="N250" s="2" t="inlineStr"/>
-      <c r="O250" s="2" t="inlineStr"/>
+      <c r="K250" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>USD 5.90 / 10</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>Ozo Keyboards</t>
+        </is>
+      </c>
+      <c r="N250" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ozokeyboards.com/products/ttc-taie-sword-magnetic-linear-switches</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P250" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=cwQAKh5wkfw</t>
@@ -17402,11 +19600,29 @@
         <v>3.45</v>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
-      <c r="K251" s="4" t="n"/>
-      <c r="L251" s="2" t="inlineStr"/>
-      <c r="M251" s="2" t="inlineStr"/>
-      <c r="N251" s="2" t="inlineStr"/>
-      <c r="O251" s="2" t="inlineStr"/>
+      <c r="K251" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>USD 11.97 / 15 (5% off with code KBDNEWS)</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>TTC store (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N251" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/TTC-MCHOSE-Noble-Horse-514.html</t>
+        </is>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P251" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=CTfBcw93MEw</t>
@@ -17464,11 +19680,29 @@
           <t>smooth, vintage</t>
         </is>
       </c>
-      <c r="K252" s="4" t="n"/>
-      <c r="L252" s="2" t="inlineStr"/>
-      <c r="M252" s="2" t="inlineStr"/>
-      <c r="N252" s="2" t="inlineStr"/>
-      <c r="O252" s="2" t="inlineStr"/>
+      <c r="K252" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.14 / 10 (TTCswitch, kbd.news table may be stale; MechanicalKeyboards USD 0.33 / 1)</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>TTCswitch</t>
+        </is>
+      </c>
+      <c r="N252" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/TTC-X-Pantheonkeys-PT-Black-521.html</t>
+        </is>
+      </c>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P252" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=3OmRz1G320M</t>
@@ -17515,10 +19749,18 @@
       <c r="I253" s="3" t="n"/>
       <c r="J253" s="2" t="inlineStr"/>
       <c r="K253" s="4" t="n"/>
-      <c r="L253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>not found (vintage, no retail listing)</t>
+        </is>
+      </c>
       <c r="M253" s="2" t="inlineStr"/>
       <c r="N253" s="2" t="inlineStr"/>
-      <c r="O253" s="2" t="inlineStr"/>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P253" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jBTtG4hDQnk</t>
@@ -17576,11 +19818,29 @@
           <t>thocky, smooth</t>
         </is>
       </c>
-      <c r="K254" s="4" t="n"/>
-      <c r="L254" s="2" t="inlineStr"/>
-      <c r="M254" s="2" t="inlineStr"/>
-      <c r="N254" s="2" t="inlineStr"/>
-      <c r="O254" s="2" t="inlineStr"/>
+      <c r="K254" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.99 / 10</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t>Lumekeebs</t>
+        </is>
+      </c>
+      <c r="N254" s="5" t="inlineStr">
+        <is>
+          <t>https://lumekeebs.com/collections/vertex-switches/products/vertex-v1-linear-switches</t>
+        </is>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P254" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oM9ObIOhPO8</t>
@@ -17638,11 +19898,29 @@
           <t>creamy</t>
         </is>
       </c>
-      <c r="K255" s="4" t="n"/>
-      <c r="L255" s="2" t="inlineStr"/>
-      <c r="M255" s="2" t="inlineStr"/>
-      <c r="N255" s="2" t="inlineStr"/>
-      <c r="O255" s="2" t="inlineStr"/>
+      <c r="K255" s="4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>USD 0.45 / 1</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>MechanicalKeyboards.com</t>
+        </is>
+      </c>
+      <c r="N255" s="5" t="inlineStr">
+        <is>
+          <t>https://mechanicalkeyboards.com/products/womier-mint-blizzard-pom-42g-linear-switch</t>
+        </is>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P255" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=zwivIYgCfDQ</t>
@@ -17682,21 +19960,45 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E256" s="2" t="n"/>
+      <c r="E256" s="2" t="n">
+        <v>35</v>
+      </c>
       <c r="F256" s="2" t="n"/>
-      <c r="G256" s="2" t="n"/>
+      <c r="G256" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="H256" s="3" t="n"/>
-      <c r="I256" s="3" t="n"/>
+      <c r="I256" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
           <t>loud, clacky</t>
         </is>
       </c>
-      <c r="K256" s="4" t="n"/>
-      <c r="L256" s="2" t="inlineStr"/>
-      <c r="M256" s="2" t="inlineStr"/>
-      <c r="N256" s="2" t="inlineStr"/>
-      <c r="O256" s="2" t="inlineStr"/>
+      <c r="K256" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>USD 1.70 / 1</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>MaxGaming US</t>
+        </is>
+      </c>
+      <c r="N256" s="5" t="inlineStr">
+        <is>
+          <t>https://us.maxgaming.com/us/switches/wuque-studio-ws-flux-clacky-he-linear-switch</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P256" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=A5pDNB00QKU</t>
@@ -17713,7 +20015,11 @@
           <t>https://www.maxgaming.com/en/switches/wuque-studio-ws-flux-clacky-he-linear-switch</t>
         </is>
       </c>
-      <c r="T256" s="2" t="inlineStr"/>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
+          <t>filled 2026-10-19 from https://us.maxgaming.com/us/switches/wuque-studio-ws-flux-clacky-he-linear-switch</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -17750,11 +20056,29 @@
           <t>deep, clacky</t>
         </is>
       </c>
-      <c r="K257" s="4" t="n"/>
-      <c r="L257" s="2" t="inlineStr"/>
-      <c r="M257" s="2" t="inlineStr"/>
-      <c r="N257" s="2" t="inlineStr"/>
-      <c r="O257" s="2" t="inlineStr"/>
+      <c r="K257" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>USD 1.70 / 1 (min qty 10)</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>MaxGaming US</t>
+        </is>
+      </c>
+      <c r="N257" s="5" t="inlineStr">
+        <is>
+          <t>https://us.maxgaming.com/us/switches/wuque-studio-ws-flux-deep-clacky-he-linear-switch</t>
+        </is>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P257" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=9io1ASH-rJo</t>
@@ -17804,11 +20128,29 @@
         <v>3.5</v>
       </c>
       <c r="J258" s="2" t="inlineStr"/>
-      <c r="K258" s="4" t="n"/>
-      <c r="L258" s="2" t="inlineStr"/>
-      <c r="M258" s="2" t="inlineStr"/>
-      <c r="N258" s="2" t="inlineStr"/>
-      <c r="O258" s="2" t="inlineStr"/>
+      <c r="K258" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>USD 1.70 / 1 (assumed per switch; Hall Effect)</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>MaxGaming US</t>
+        </is>
+      </c>
+      <c r="N258" s="5" t="inlineStr">
+        <is>
+          <t>https://us.maxgaming.com/us/switches/wuque-studio-ws-flux-pink-lotus-he-linear-switch</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P258" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=aalL2YBsYJ0</t>
@@ -17861,12 +20203,34 @@
       <c r="I259" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J259" s="2" t="inlineStr"/>
-      <c r="K259" s="4" t="n"/>
-      <c r="L259" s="2" t="inlineStr"/>
-      <c r="M259" s="2" t="inlineStr"/>
-      <c r="N259" s="2" t="inlineStr"/>
-      <c r="O259" s="2" t="inlineStr"/>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>low-pitched, muted, thocky</t>
+        </is>
+      </c>
+      <c r="K259" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.90 / 10</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N259" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/ws-morandi-vs-ws-red</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P259" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GhwBMSVmvdo</t>
@@ -17920,11 +20284,29 @@
         <v>3.8</v>
       </c>
       <c r="J260" s="2" t="inlineStr"/>
-      <c r="K260" s="4" t="n"/>
-      <c r="L260" s="2" t="inlineStr"/>
-      <c r="M260" s="2" t="inlineStr"/>
-      <c r="N260" s="2" t="inlineStr"/>
-      <c r="O260" s="2" t="inlineStr"/>
+      <c r="K260" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>USD 13.65 / 35</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>Wuque Studio store (via kbd.news)</t>
+        </is>
+      </c>
+      <c r="N260" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/Wuque-Studio-WS-Quartz-340.html</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P260" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=gsnEJ1NZdsI</t>
@@ -17976,11 +20358,29 @@
         <v>3.8</v>
       </c>
       <c r="J261" s="2" t="inlineStr"/>
-      <c r="K261" s="4" t="n"/>
-      <c r="L261" s="2" t="inlineStr"/>
-      <c r="M261" s="2" t="inlineStr"/>
-      <c r="N261" s="2" t="inlineStr"/>
-      <c r="O261" s="2" t="inlineStr"/>
+      <c r="K261" s="4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>USD 3.50 / 10</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>Milktooth</t>
+        </is>
+      </c>
+      <c r="N261" s="5" t="inlineStr">
+        <is>
+          <t>https://milktooth.com/comparisons/ws-pearl-vs-ws-yellow</t>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P261" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WX_kacd80YM</t>
@@ -18038,11 +20438,29 @@
           <t>silent</t>
         </is>
       </c>
-      <c r="K262" s="4" t="n"/>
-      <c r="L262" s="2" t="inlineStr"/>
-      <c r="M262" s="2" t="inlineStr"/>
-      <c r="N262" s="2" t="inlineStr"/>
-      <c r="O262" s="2" t="inlineStr"/>
+      <c r="K262" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>USD 62.99 / 105 (with KBDNEWS 10% code)</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>XVX Keyboard</t>
+        </is>
+      </c>
+      <c r="N262" s="5" t="inlineStr">
+        <is>
+          <t>https://kbd.news/switch/XVX-Whisper-EC-HE-switch-560.html</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P262" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZkCokoGgAGA</t>
@@ -18082,23 +20500,47 @@
           <t>MX</t>
         </is>
       </c>
-      <c r="E263" s="2" t="n"/>
+      <c r="E263" s="2" t="n">
+        <v>62</v>
+      </c>
       <c r="F263" s="2" t="n"/>
       <c r="G263" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="H263" s="3" t="n"/>
-      <c r="I263" s="3" t="n"/>
+      <c r="H263" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
           <t>thocky</t>
         </is>
       </c>
-      <c r="K263" s="4" t="n"/>
-      <c r="L263" s="2" t="inlineStr"/>
-      <c r="M263" s="2" t="inlineStr"/>
-      <c r="N263" s="2" t="inlineStr"/>
-      <c r="O263" s="2" t="inlineStr"/>
+      <c r="K263" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>USD 8.00 / 10 (62g in stock; 65/67/78g sold out)</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>ZealPC</t>
+        </is>
+      </c>
+      <c r="N263" s="5" t="inlineStr">
+        <is>
+          <t>https://zealpc.net/products/zealio</t>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="P263" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=nKDHGk1Fg28</t>
@@ -18117,7 +20559,7 @@
       </c>
       <c r="T263" s="2" t="inlineStr">
         <is>
-          <t>bottom-out: 62/65/67/78</t>
+          <t>bottom-out: 62/65/67/78; filled 2026-10-19 from https://mkbguide.com/blog/zealpc-switches-deep-dive-guide</t>
         </is>
       </c>
     </row>
@@ -18358,137 +20800,254 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N132" r:id="rId233"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P158" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P159" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P160" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P161" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P162" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P163" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P164" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P165" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P166" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P167" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P168" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P169" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P170" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P171" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P172" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P173" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P174" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P175" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P176" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P177" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P178" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P179" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P180" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P181" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P182" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P183" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P184" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P185" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P186" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P187" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P188" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P189" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P190" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P191" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P192" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P193" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P194" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P195" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P196" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P197" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P198" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P199" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P200" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P201" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P202" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P203" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P204" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P205" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P206" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P207" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P208" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P209" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P210" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P211" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P212" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P213" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P214" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P215" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P216" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P217" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P218" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P219" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P220" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P221" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P222" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P223" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P224" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P225" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P226" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P227" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P228" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P229" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P230" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P231" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P232" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P233" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P234" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P235" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P236" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P237" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P238" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P239" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P240" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P241" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P242" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P243" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P244" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P245" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P246" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P247" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P248" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P249" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P250" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P251" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P252" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P253" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P254" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P255" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P256" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P257" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P258" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P259" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P260" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P261" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P262" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P263" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N133" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N134" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N135" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N136" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N137" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N138" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N139" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N140" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N141" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N142" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N143" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N145" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N147" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N149" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N150" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N152" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N153" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N155" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N157" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N158" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P158" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N159" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P159" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N160" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P160" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N161" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P161" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N162" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P162" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N163" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P163" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N164" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P164" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N165" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P165" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N166" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P166" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N167" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P167" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N168" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P168" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N169" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P169" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N170" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P170" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N171" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P171" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N172" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P172" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N173" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P173" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N174" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P174" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N175" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P175" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P176" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N177" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P177" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N178" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P178" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P179" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N180" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P180" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N181" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P181" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N182" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P182" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N183" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P183" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N184" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P184" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N185" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P185" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N186" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P186" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N187" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P187" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N188" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P188" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N189" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P189" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P190" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N191" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P191" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N192" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P192" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P193" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N194" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P194" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N195" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P195" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N196" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P196" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N197" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P197" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P198" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N199" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P199" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N200" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P200" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N201" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P201" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N202" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P202" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N203" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P203" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N204" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P204" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P205" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N206" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P206" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N207" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P207" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N208" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P208" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N209" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P209" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N210" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P210" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N211" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P211" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N212" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P212" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P213" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P214" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N215" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P215" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N216" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P216" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N217" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P217" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N218" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P218" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N219" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P219" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N220" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P220" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N221" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P221" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N222" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P222" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N223" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P223" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N224" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P224" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N225" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P225" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N226" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P226" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N227" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P227" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P228" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N229" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P229" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N230" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P230" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N231" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P231" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N232" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P232" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P233" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N234" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P234" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N235" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P235" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N236" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P236" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P237" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N238" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P238" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N239" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P239" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N240" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P240" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P241" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N242" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P242" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N243" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P243" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N244" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P244" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N245" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P245" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N246" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P246" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N247" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P247" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N248" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P248" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N249" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P249" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N250" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P250" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N251" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P251" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N252" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P252" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P253" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N254" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P254" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N255" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P255" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N256" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P256" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N257" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P257" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N258" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P258" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N259" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P259" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N260" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P260" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N261" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P261" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N262" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P262" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N263" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P263" r:id="rId482"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18558,7 +21117,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Price: CAD per single switch, checked 2026-10-19. Canadian price when found, otherwise the cheapest major retailer in USD converted at 1.40 CAD per USD (mid-market about 1.39 to 1.41 that day). Price as listed keeps the original amount, pack size and any sold-out, discount-code or variant caveat. Round 1 covers the first 131 rows; the rest are priced in round 2.</t>
+          <t>Price: CAD per single switch, checked 2026-10-19. Canadian price when found, otherwise the cheapest major retailer in USD converted at 1.40 CAD per USD (mid-market about 1.39 to 1.41 that day). Price as listed keeps the original amount, pack size and any sold-out, discount-code or variant caveat. Rounds 1 and 2 cover every row; a recheck of prices is planned.</t>
         </is>
       </c>
     </row>
